--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T05:11:07+00:00</t>
+    <t>2026-03-16T07:24:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T07:24:26+00:00</t>
+    <t>2026-03-16T20:48:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:48:05+00:00</t>
+    <t>2026-03-16T20:59:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T20:59:47+00:00</t>
+    <t>2026-03-16T21:16:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:16:15+00:00</t>
+    <t>2026-03-16T21:44:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:44:19+00:00</t>
+    <t>2026-03-16T21:58:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T21:58:37+00:00</t>
+    <t>2026-03-16T22:06:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:06:54+00:00</t>
+    <t>2026-03-16T22:26:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-16T22:26:22+00:00</t>
+    <t>2026-03-19T20:53:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T20:53:49+00:00</t>
+    <t>2026-03-19T21:27:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-19T21:27:42+00:00</t>
+    <t>2026-04-08T04:20:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -10,13 +10,13 @@
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$47</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AN$38</definedName>
   </definedNames>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1744" uniqueCount="417">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1421" uniqueCount="308">
   <si>
     <t>Property</t>
   </si>
@@ -33,7 +33,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>0.1.0</t>
+    <t>0.2.0</t>
   </si>
   <si>
     <t>Name</t>
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T04:20:57+00:00</t>
+    <t>2026-04-10T05:32:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -513,501 +513,70 @@
     <t>NhfrCode</t>
   </si>
   <si>
-    <t>DOH NHFR Code</t>
-  </si>
-  <si>
-    <t>Philippines Department of Health National Health Facilities Registry Code</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.id</t>
-  </si>
-  <si>
-    <t xml:space="preserve">string
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-doh-nhfr-code}
 </t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
-  </si>
-  <si>
-    <t>Element.id</t>
-  </si>
-  <si>
-    <t>n/a</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.extension</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">value:url}
+    <t>Organization.identifier:PAN</t>
+  </si>
+  <si>
+    <t>PAN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-philhealth-pan}
 </t>
   </si>
   <si>
-    <t>Extensions are always sliced by (at least) url</t>
-  </si>
-  <si>
-    <t>Element.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.use</t>
-  </si>
-  <si>
-    <t>Organization.identifier.use</t>
-  </si>
-  <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
-  </si>
-  <si>
-    <t>official</t>
-  </si>
-  <si>
-    <t>required</t>
-  </si>
-  <si>
-    <t>Identifies the purpose for this identifier, if known .</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-use|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.use</t>
-  </si>
-  <si>
-    <t>Role.code or implied by context</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type</t>
+    <t>Organization.identifier:PEN</t>
+  </si>
+  <si>
+    <t>PEN</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Identifier {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-philhealth-pen}
+</t>
+  </si>
+  <si>
+    <t>Organization.active</t>
+  </si>
+  <si>
+    <t xml:space="preserve">boolean
+</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use</t>
+  </si>
+  <si>
+    <t>Whether the organization's record is still in active use.</t>
+  </si>
+  <si>
+    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
+This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
+  </si>
+  <si>
+    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
+  </si>
+  <si>
+    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
+  </si>
+  <si>
+    <t>No equivalent in HL7 v2</t>
+  </si>
+  <si>
+    <t>.status</t>
+  </si>
+  <si>
+    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
+  </si>
+  <si>
+    <t>FiveWs.status</t>
+  </si>
+  <si>
+    <t>Organization.type</t>
   </si>
   <si>
     <t xml:space="preserve">CodeableConcept
 </t>
-  </si>
-  <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
-  </si>
-  <si>
-    <t>extensible</t>
-  </si>
-  <si>
-    <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
-  </si>
-  <si>
-    <t>Identifier.type</t>
-  </si>
-  <si>
-    <t>CX.5</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coding
-</t>
-  </si>
-  <si>
-    <t>Code defined by a terminology system</t>
-  </si>
-  <si>
-    <t>A reference to a code defined by a terminology system.</t>
-  </si>
-  <si>
-    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
-  </si>
-  <si>
-    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.coding</t>
-  </si>
-  <si>
-    <t>C*E.1-8, C*E.10-22</t>
-  </si>
-  <si>
-    <t>union(., ./translation)</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.id</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.extension</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.system</t>
-  </si>
-  <si>
-    <t>Identity of the terminology system</t>
-  </si>
-  <si>
-    <t>The identification of the code system that defines the meaning of the symbol in the code.</t>
-  </si>
-  <si>
-    <t>The URI may be an OID (urn:oid:...) or a UUID (urn:uuid:...).  OIDs and UUIDs SHALL be references to the HL7 OID registry. Otherwise, the URI should come from HL7's list of FHIR defined special URIs or it should reference to some definition that establishes the system clearly and unambiguously.</t>
-  </si>
-  <si>
-    <t>Need to be unambiguous about the source of the definition of the symbol.</t>
-  </si>
-  <si>
-    <t>http://terminology.hl7.org/CodeSystem/v2-0203</t>
-  </si>
-  <si>
-    <t>Coding.system</t>
-  </si>
-  <si>
-    <t>C*E.3</t>
-  </si>
-  <si>
-    <t>./codeSystem</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.version</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.version</t>
-  </si>
-  <si>
-    <t>Version of the system - if relevant</t>
-  </si>
-  <si>
-    <t>The version of the code system which was used when choosing this code. Note that a well-maintained code system does not need the version reported, because the meaning of codes is consistent across versions. However this cannot consistently be assured, and when the meaning is not guaranteed to be consistent, the version SHOULD be exchanged.</t>
-  </si>
-  <si>
-    <t>Where the terminology does not clearly define what string should be used to identify code system versions, the recommendation is to use the date (expressed in FHIR date format) on which that version was officially published as the version date.</t>
-  </si>
-  <si>
-    <t>Coding.version</t>
-  </si>
-  <si>
-    <t>C*E.7</t>
-  </si>
-  <si>
-    <t>./codeSystemVersion</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.code</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.code</t>
-  </si>
-  <si>
-    <t>Symbol in syntax defined by the system</t>
-  </si>
-  <si>
-    <t>A symbol in syntax defined by the system. The symbol may be a predefined code or an expression in a syntax defined by the coding system (e.g. post-coordination).</t>
-  </si>
-  <si>
-    <t>Need to refer to a particular code in the system.</t>
-  </si>
-  <si>
-    <t>FI</t>
-  </si>
-  <si>
-    <t>Coding.code</t>
-  </si>
-  <si>
-    <t>C*E.1</t>
-  </si>
-  <si>
-    <t>./code</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.display</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.display</t>
-  </si>
-  <si>
-    <t>Representation defined by the system</t>
-  </si>
-  <si>
-    <t>A representation of the meaning of the code in the system, following the rules of the system.</t>
-  </si>
-  <si>
-    <t>Need to be able to carry a human-readable meaning of the code for readers that do not know  the system.</t>
-  </si>
-  <si>
-    <t>Coding.display</t>
-  </si>
-  <si>
-    <t>C*E.2 - but note this is not well followed</t>
-  </si>
-  <si>
-    <t>CV.displayName</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.coding.userSelected</t>
-  </si>
-  <si>
-    <t xml:space="preserve">boolean
-</t>
-  </si>
-  <si>
-    <t>If this coding was chosen directly by the user</t>
-  </si>
-  <si>
-    <t>Indicates that this coding was chosen by a user directly - e.g. off a pick list of available items (codes or displays).</t>
-  </si>
-  <si>
-    <t>Amongst a set of alternatives, a directly chosen code is the most appropriate starting point for new translations. There is some ambiguity about what exactly 'directly chosen' implies, and trading partner agreement may be needed to clarify the use of this element and its consequences more completely.</t>
-  </si>
-  <si>
-    <t>This has been identified as a clinical safety criterium - that this exact system/code pair was chosen explicitly, rather than inferred by the system based on some rules or language processing.</t>
-  </si>
-  <si>
-    <t>Coding.userSelected</t>
-  </si>
-  <si>
-    <t>Sometimes implied by being first</t>
-  </si>
-  <si>
-    <t>CD.codingRationale</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.type.text</t>
-  </si>
-  <si>
-    <t>Organization.identifier.type.text</t>
-  </si>
-  <si>
-    <t>Plain text representation of the concept</t>
-  </si>
-  <si>
-    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
-  </si>
-  <si>
-    <t>Very often the text is the same as a displayName of one of the codings.</t>
-  </si>
-  <si>
-    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
-  </si>
-  <si>
-    <t>CodeableConcept.text</t>
-  </si>
-  <si>
-    <t>C*E.9. But note many systems use C*E.2 for this</t>
-  </si>
-  <si>
-    <t>./originalText[mediaType/code="text/plain"]/data</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.system</t>
-  </si>
-  <si>
-    <t>Organization.identifier.system</t>
-  </si>
-  <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
-  </si>
-  <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
-  </si>
-  <si>
-    <t>http://doh.gov.ph/fhir/Identifier/doh-nhfr-code</t>
-  </si>
-  <si>
-    <t>http://www.acme.com/identifiers/patient</t>
-  </si>
-  <si>
-    <t>Identifier.system</t>
-  </si>
-  <si>
-    <t>CX.4 / EI-2-4</t>
-  </si>
-  <si>
-    <t>II.root or Role.id.root</t>
-  </si>
-  <si>
-    <t>./IdentifierType</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.value</t>
-  </si>
-  <si>
-    <t>Organization.identifier.value</t>
-  </si>
-  <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
-  </si>
-  <si>
-    <t>123456</t>
-  </si>
-  <si>
-    <t>Identifier.value</t>
-  </si>
-  <si>
-    <t>CX.1 / EI.1</t>
-  </si>
-  <si>
-    <t>II.extension or II.root if system indicates OID or GUID (Or Role.id.extension or root)</t>
-  </si>
-  <si>
-    <t>./Value</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.period</t>
-  </si>
-  <si>
-    <t>Organization.identifier.period</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Period
-</t>
-  </si>
-  <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
-  </si>
-  <si>
-    <t>Identifier.period</t>
-  </si>
-  <si>
-    <t>CX.7 + CX.8</t>
-  </si>
-  <si>
-    <t>Role.effectiveTime or implied by context</t>
-  </si>
-  <si>
-    <t>./StartDate and ./EndDate</t>
-  </si>
-  <si>
-    <t>Organization.identifier:NhfrCode.assigner</t>
-  </si>
-  <si>
-    <t>Organization.identifier.assigner</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
-</t>
-  </si>
-  <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
-  </si>
-  <si>
-    <t>Identifier.assigner</t>
-  </si>
-  <si>
-    <t>CX.4 / (CX.4,CX.9,CX.10)</t>
-  </si>
-  <si>
-    <t>II.assigningAuthorityName but note that this is an improper use by the definition of the field.  Also Role.scoper</t>
-  </si>
-  <si>
-    <t>./IdentifierIssuingAuthority</t>
-  </si>
-  <si>
-    <t>Organization.active</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use</t>
-  </si>
-  <si>
-    <t>Whether the organization's record is still in active use.</t>
-  </si>
-  <si>
-    <t>This active flag is not intended to be used to mark an organization as temporarily closed or under construction. Instead the Location(s) within the Organization should have the suspended status. If further details of the reason for the suspension are required, then an extension on this element should be used.
-This element is labeled as a modifier because it may be used to mark that the resource was created in error.</t>
-  </si>
-  <si>
-    <t>Need a flag to indicate a record is no longer to be used and should generally be hidden for the user in the UI.</t>
-  </si>
-  <si>
-    <t>This resource is generally assumed to be active if no value is provided for the active element</t>
-  </si>
-  <si>
-    <t>No equivalent in HL7 v2</t>
-  </si>
-  <si>
-    <t>.status</t>
-  </si>
-  <si>
-    <t>./Status (however this concept in ServD more covers why the organization is active or not, could be delisted, deregistered, not operational yet) this could alternatively be derived from ./StartDate and ./EndDate and given a context date.</t>
-  </si>
-  <si>
-    <t>FiveWs.status</t>
-  </si>
-  <si>
-    <t>Organization.type</t>
   </si>
   <si>
     <t>Kind of organization</t>
@@ -1039,7 +608,94 @@
     <t>.code</t>
   </si>
   <si>
+    <t>n/a</t>
+  </si>
+  <si>
     <t>FiveWs.class</t>
+  </si>
+  <si>
+    <t>Organization.type.id</t>
+  </si>
+  <si>
+    <t xml:space="preserve">string
+</t>
+  </si>
+  <si>
+    <t>Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+  </si>
+  <si>
+    <t>Element.id</t>
+  </si>
+  <si>
+    <t>Organization.type.extension</t>
+  </si>
+  <si>
+    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:url}
+</t>
+  </si>
+  <si>
+    <t>Extensions are always sliced by (at least) url</t>
+  </si>
+  <si>
+    <t>Element.extension</t>
+  </si>
+  <si>
+    <t>Organization.type.coding</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coding
+</t>
+  </si>
+  <si>
+    <t>Code defined by a terminology system</t>
+  </si>
+  <si>
+    <t>A reference to a code defined by a terminology system.</t>
+  </si>
+  <si>
+    <t>Codes may be defined very casually in enumerations, or code lists, up to very formal definitions such as SNOMED CT - see the HL7 v3 Core Principles for more information.  Ordering of codings is undefined and SHALL NOT be used to infer meaning. Generally, at most only one of the coding values will be labeled as UserSelected = true.</t>
+  </si>
+  <si>
+    <t>Allows for alternative encodings within a code system, and translations to other code systems.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.coding</t>
+  </si>
+  <si>
+    <t>C*E.1-8, C*E.10-22</t>
+  </si>
+  <si>
+    <t>union(., ./translation)</t>
+  </si>
+  <si>
+    <t>Organization.type.text</t>
+  </si>
+  <si>
+    <t>Plain text representation of the concept</t>
+  </si>
+  <si>
+    <t>A human language representation of the concept as seen/selected/uttered by the user who entered the data and/or which represents the intended meaning of the user.</t>
+  </si>
+  <si>
+    <t>Very often the text is the same as a displayName of one of the codings.</t>
+  </si>
+  <si>
+    <t>The codes from the terminologies do not always capture the correct meaning with all the nuances of the human using them, or sometimes there is no appropriate code at all. In these cases, the text is used to capture the full meaning of the source.</t>
+  </si>
+  <si>
+    <t>CodeableConcept.text</t>
+  </si>
+  <si>
+    <t>C*E.9. But note many systems use C*E.2 for this</t>
+  </si>
+  <si>
+    <t>./originalText[mediaType/code="text/plain"]/data</t>
   </si>
   <si>
     <t>Organization.name</t>
@@ -1121,7 +777,7 @@
     <t>Organization.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address|Address}
+    <t xml:space="preserve">Address {http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-address}
 </t>
   </si>
   <si>
@@ -1157,6 +813,10 @@
     <t>Organization.partOf</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://doh.gov.ph/fhir/ph-core/StructureDefinition/ph-core-organization)
+</t>
+  </si>
+  <si>
     <t>The organization of which this organization forms a part</t>
   </si>
   <si>
@@ -1226,6 +886,9 @@
     <t>Need to distinguish between multiple contact persons.</t>
   </si>
   <si>
+    <t>extensible</t>
+  </si>
+  <si>
     <t>The purpose for which you would contact a contact party.</t>
   </si>
   <si>
@@ -1233,6 +896,18 @@
   </si>
   <si>
     <t>./type</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.id</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.extension</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.coding</t>
+  </si>
+  <si>
+    <t>Organization.contact.purpose.text</t>
   </si>
   <si>
     <t>Organization.contact.name</t>
@@ -1623,11 +1298,11 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AN47"/>
+  <dimension ref="A1:AN38"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.95703125" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="39.03125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="32.42578125" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="32.42578125" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="10.8515625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
@@ -1636,7 +1311,7 @@
     <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="68.703125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="67.7734375" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1645,12 +1320,12 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="8.53515625" customWidth="true" bestFit="true"/>
     <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="84.33984375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="46.38671875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="41.5390625" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
@@ -1662,7 +1337,7 @@
     <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
     <col min="37" max="37" width="39.109375" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="87.9765625" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="43.6953125" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="187.0625" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="31.65234375" customWidth="true" bestFit="true"/>
   </cols>
@@ -2957,13 +2632,13 @@
         <v>88</v>
       </c>
       <c r="K12" t="s" s="2">
-        <v>145</v>
+        <v>159</v>
       </c>
       <c r="L12" t="s" s="2">
-        <v>159</v>
+        <v>146</v>
       </c>
       <c r="M12" t="s" s="2">
-        <v>160</v>
+        <v>147</v>
       </c>
       <c r="N12" s="2"/>
       <c r="O12" t="s" s="2">
@@ -3043,14 +2718,16 @@
         <v>156</v>
       </c>
     </row>
-    <row r="13" hidden="true">
+    <row r="13">
       <c r="A13" t="s" s="2">
+        <v>160</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>144</v>
+      </c>
+      <c r="C13" t="s" s="2">
         <v>161</v>
       </c>
-      <c r="B13" t="s" s="2">
-        <v>162</v>
-      </c>
-      <c r="C13" s="2"/>
       <c r="D13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3059,28 +2736,30 @@
         <v>78</v>
       </c>
       <c r="G13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I13" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J13" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K13" t="s" s="2">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="L13" t="s" s="2">
-        <v>164</v>
+        <v>146</v>
       </c>
       <c r="M13" t="s" s="2">
-        <v>165</v>
+        <v>147</v>
       </c>
       <c r="N13" s="2"/>
-      <c r="O13" s="2"/>
+      <c r="O13" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P13" t="s" s="2">
         <v>77</v>
       </c>
@@ -3128,43 +2807,45 @@
         <v>77</v>
       </c>
       <c r="AF13" t="s" s="2">
-        <v>166</v>
+        <v>144</v>
       </c>
       <c r="AG13" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH13" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI13" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ13" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK13" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL13" t="s" s="2">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="AM13" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AN13" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="14" hidden="true">
+    <row r="14">
       <c r="A14" t="s" s="2">
-        <v>168</v>
+        <v>163</v>
       </c>
       <c r="B14" t="s" s="2">
-        <v>169</v>
-      </c>
-      <c r="C14" s="2"/>
+        <v>144</v>
+      </c>
+      <c r="C14" t="s" s="2">
+        <v>164</v>
+      </c>
       <c r="D14" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E14" s="2"/>
       <c r="F14" t="s" s="2">
@@ -3174,27 +2855,27 @@
         <v>79</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J14" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K14" t="s" s="2">
-        <v>133</v>
+        <v>165</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>134</v>
+        <v>146</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N14" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O14" s="2"/>
+        <v>147</v>
+      </c>
+      <c r="N14" s="2"/>
+      <c r="O14" t="s" s="2">
+        <v>148</v>
+      </c>
       <c r="P14" t="s" s="2">
         <v>77</v>
       </c>
@@ -3230,19 +2911,19 @@
         <v>77</v>
       </c>
       <c r="AB14" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC14" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD14" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE14" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF14" t="s" s="2">
-        <v>173</v>
+        <v>144</v>
       </c>
       <c r="AG14" t="s" s="2">
         <v>78</v>
@@ -3251,30 +2932,30 @@
         <v>79</v>
       </c>
       <c r="AI14" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ14" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK14" t="s" s="2">
-        <v>77</v>
+        <v>153</v>
       </c>
       <c r="AL14" t="s" s="2">
-        <v>167</v>
+        <v>154</v>
       </c>
       <c r="AM14" t="s" s="2">
-        <v>77</v>
+        <v>155</v>
       </c>
       <c r="AN14" t="s" s="2">
-        <v>77</v>
+        <v>156</v>
       </c>
     </row>
-    <row r="15" hidden="true">
+    <row r="15">
       <c r="A15" t="s" s="2">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>175</v>
+        <v>166</v>
       </c>
       <c r="C15" s="2"/>
       <c r="D15" t="s" s="2">
@@ -3288,7 +2969,7 @@
         <v>87</v>
       </c>
       <c r="H15" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I15" t="s" s="2">
         <v>88</v>
@@ -3297,29 +2978,31 @@
         <v>88</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>107</v>
+        <v>167</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="N15" t="s" s="2">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="O15" t="s" s="2">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="P15" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q15" s="2"/>
+      <c r="Q15" t="s" s="2">
+        <v>172</v>
+      </c>
       <c r="R15" t="s" s="2">
         <v>77</v>
       </c>
       <c r="S15" t="s" s="2">
-        <v>180</v>
+        <v>77</v>
       </c>
       <c r="T15" t="s" s="2">
         <v>77</v>
@@ -3334,13 +3017,13 @@
         <v>77</v>
       </c>
       <c r="X15" t="s" s="2">
-        <v>181</v>
+        <v>77</v>
       </c>
       <c r="Y15" t="s" s="2">
-        <v>182</v>
+        <v>77</v>
       </c>
       <c r="Z15" t="s" s="2">
-        <v>183</v>
+        <v>77</v>
       </c>
       <c r="AA15" t="s" s="2">
         <v>77</v>
@@ -3358,7 +3041,7 @@
         <v>77</v>
       </c>
       <c r="AF15" t="s" s="2">
-        <v>184</v>
+        <v>166</v>
       </c>
       <c r="AG15" t="s" s="2">
         <v>78</v>
@@ -3373,24 +3056,24 @@
         <v>99</v>
       </c>
       <c r="AK15" t="s" s="2">
-        <v>130</v>
+        <v>173</v>
       </c>
       <c r="AL15" t="s" s="2">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="AM15" t="s" s="2">
-        <v>77</v>
+        <v>175</v>
       </c>
       <c r="AN15" t="s" s="2">
-        <v>77</v>
+        <v>176</v>
       </c>
     </row>
-    <row r="16" hidden="true">
+    <row r="16">
       <c r="A16" t="s" s="2">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C16" s="2"/>
       <c r="D16" t="s" s="2">
@@ -3401,10 +3084,10 @@
         <v>78</v>
       </c>
       <c r="G16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H16" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I16" t="s" s="2">
         <v>77</v>
@@ -3413,19 +3096,19 @@
         <v>88</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="N16" t="s" s="2">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="O16" t="s" s="2">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="P16" t="s" s="2">
         <v>77</v>
@@ -3450,13 +3133,13 @@
         <v>77</v>
       </c>
       <c r="X16" t="s" s="2">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="Y16" t="s" s="2">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="Z16" t="s" s="2">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="AA16" t="s" s="2">
         <v>77</v>
@@ -3474,13 +3157,13 @@
         <v>77</v>
       </c>
       <c r="AF16" t="s" s="2">
-        <v>196</v>
+        <v>177</v>
       </c>
       <c r="AG16" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH16" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI16" t="s" s="2">
         <v>77</v>
@@ -3489,24 +3172,24 @@
         <v>99</v>
       </c>
       <c r="AK16" t="s" s="2">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="AL16" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="AM16" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AN16" t="s" s="2">
-        <v>77</v>
+        <v>189</v>
       </c>
     </row>
     <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
-        <v>198</v>
+        <v>190</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
@@ -3529,13 +3212,13 @@
         <v>77</v>
       </c>
       <c r="K17" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>164</v>
+        <v>192</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>165</v>
+        <v>193</v>
       </c>
       <c r="N17" s="2"/>
       <c r="O17" s="2"/>
@@ -3586,7 +3269,7 @@
         <v>77</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>166</v>
+        <v>194</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>78</v>
@@ -3604,7 +3287,7 @@
         <v>77</v>
       </c>
       <c r="AL17" t="s" s="2">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AM17" t="s" s="2">
         <v>77</v>
@@ -3615,10 +3298,10 @@
     </row>
     <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
-        <v>200</v>
+        <v>195</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>201</v>
+        <v>195</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
@@ -3647,7 +3330,7 @@
         <v>134</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>170</v>
+        <v>196</v>
       </c>
       <c r="N18" t="s" s="2">
         <v>136</v>
@@ -3688,10 +3371,10 @@
         <v>77</v>
       </c>
       <c r="AB18" t="s" s="2">
-        <v>171</v>
+        <v>197</v>
       </c>
       <c r="AC18" t="s" s="2">
-        <v>172</v>
+        <v>198</v>
       </c>
       <c r="AD18" t="s" s="2">
         <v>77</v>
@@ -3700,7 +3383,7 @@
         <v>151</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>173</v>
+        <v>199</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>78</v>
@@ -3718,7 +3401,7 @@
         <v>77</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>167</v>
+        <v>188</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>77</v>
@@ -3727,12 +3410,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="19" hidden="true">
+    <row r="19">
       <c r="A19" t="s" s="2">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -3746,7 +3429,7 @@
         <v>79</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>77</v>
@@ -3755,19 +3438,19 @@
         <v>88</v>
       </c>
       <c r="K19" t="s" s="2">
+        <v>201</v>
+      </c>
+      <c r="L19" t="s" s="2">
+        <v>202</v>
+      </c>
+      <c r="M19" t="s" s="2">
+        <v>203</v>
+      </c>
+      <c r="N19" t="s" s="2">
         <v>204</v>
       </c>
-      <c r="L19" t="s" s="2">
+      <c r="O19" t="s" s="2">
         <v>205</v>
-      </c>
-      <c r="M19" t="s" s="2">
-        <v>206</v>
-      </c>
-      <c r="N19" t="s" s="2">
-        <v>207</v>
-      </c>
-      <c r="O19" t="s" s="2">
-        <v>208</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>77</v>
@@ -3816,7 +3499,7 @@
         <v>77</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>78</v>
@@ -3831,10 +3514,10 @@
         <v>99</v>
       </c>
       <c r="AK19" t="s" s="2">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="AL19" t="s" s="2">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="AM19" t="s" s="2">
         <v>77</v>
@@ -3843,12 +3526,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="20" hidden="true">
+    <row r="20">
       <c r="A20" t="s" s="2">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>213</v>
+        <v>209</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -3862,25 +3545,29 @@
         <v>87</v>
       </c>
       <c r="H20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I20" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J20" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K20" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>164</v>
+        <v>210</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N20" s="2"/>
-      <c r="O20" s="2"/>
+        <v>211</v>
+      </c>
+      <c r="N20" t="s" s="2">
+        <v>212</v>
+      </c>
+      <c r="O20" t="s" s="2">
+        <v>213</v>
+      </c>
       <c r="P20" t="s" s="2">
         <v>77</v>
       </c>
@@ -3928,7 +3615,7 @@
         <v>77</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>166</v>
+        <v>214</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>78</v>
@@ -3940,13 +3627,13 @@
         <v>77</v>
       </c>
       <c r="AJ20" t="s" s="2">
-        <v>77</v>
+        <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>77</v>
+        <v>215</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>167</v>
+        <v>216</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>77</v>
@@ -3955,46 +3642,48 @@
         <v>77</v>
       </c>
     </row>
-    <row r="21" hidden="true">
+    <row r="21">
       <c r="A21" t="s" s="2">
-        <v>214</v>
+        <v>217</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
-        <v>132</v>
+        <v>77</v>
       </c>
       <c r="E21" s="2"/>
       <c r="F21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J21" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>133</v>
+        <v>191</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>134</v>
+        <v>218</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>170</v>
+        <v>219</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O21" s="2"/>
+        <v>220</v>
+      </c>
+      <c r="O21" t="s" s="2">
+        <v>221</v>
+      </c>
       <c r="P21" t="s" s="2">
         <v>77</v>
       </c>
@@ -4030,40 +3719,40 @@
         <v>77</v>
       </c>
       <c r="AB21" t="s" s="2">
-        <v>171</v>
+        <v>77</v>
       </c>
       <c r="AC21" t="s" s="2">
-        <v>172</v>
+        <v>77</v>
       </c>
       <c r="AD21" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE21" t="s" s="2">
-        <v>151</v>
+        <v>77</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>173</v>
+        <v>217</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH21" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI21" t="s" s="2">
-        <v>77</v>
+        <v>152</v>
       </c>
       <c r="AJ21" t="s" s="2">
-        <v>138</v>
+        <v>99</v>
       </c>
       <c r="AK21" t="s" s="2">
-        <v>77</v>
+        <v>222</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>167</v>
+        <v>223</v>
       </c>
       <c r="AM21" t="s" s="2">
-        <v>77</v>
+        <v>224</v>
       </c>
       <c r="AN21" t="s" s="2">
         <v>77</v>
@@ -4071,10 +3760,10 @@
     </row>
     <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
-        <v>216</v>
+        <v>225</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -4085,7 +3774,7 @@
         <v>78</v>
       </c>
       <c r="G22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H22" t="s" s="2">
         <v>77</v>
@@ -4094,29 +3783,29 @@
         <v>77</v>
       </c>
       <c r="J22" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>101</v>
+        <v>191</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q22" s="2"/>
       <c r="R22" t="s" s="2">
-        <v>222</v>
+        <v>77</v>
       </c>
       <c r="S22" t="s" s="2">
         <v>77</v>
@@ -4158,13 +3847,13 @@
         <v>77</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH22" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI22" t="s" s="2">
         <v>77</v>
@@ -4173,10 +3862,10 @@
         <v>99</v>
       </c>
       <c r="AK22" t="s" s="2">
-        <v>224</v>
+        <v>77</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>77</v>
@@ -4185,12 +3874,12 @@
         <v>77</v>
       </c>
     </row>
-    <row r="23" hidden="true">
+    <row r="23">
       <c r="A23" t="s" s="2">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>227</v>
+        <v>230</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -4201,30 +3890,32 @@
         <v>78</v>
       </c>
       <c r="G23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H23" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I23" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J23" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K23" t="s" s="2">
-        <v>163</v>
+        <v>231</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="N23" t="s" s="2">
-        <v>230</v>
-      </c>
-      <c r="O23" s="2"/>
+        <v>234</v>
+      </c>
+      <c r="O23" t="s" s="2">
+        <v>235</v>
+      </c>
       <c r="P23" t="s" s="2">
         <v>77</v>
       </c>
@@ -4272,39 +3963,39 @@
         <v>77</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH23" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI23" t="s" s="2">
-        <v>77</v>
+        <v>236</v>
       </c>
       <c r="AJ23" t="s" s="2">
-        <v>99</v>
+        <v>237</v>
       </c>
       <c r="AK23" t="s" s="2">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="AM23" t="s" s="2">
-        <v>77</v>
+        <v>240</v>
       </c>
       <c r="AN23" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="24" hidden="true">
+    <row r="24">
       <c r="A24" t="s" s="2">
-        <v>234</v>
+        <v>241</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -4315,36 +4006,38 @@
         <v>78</v>
       </c>
       <c r="G24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J24" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>107</v>
+        <v>242</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>236</v>
+        <v>243</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>237</v>
-      </c>
-      <c r="N24" s="2"/>
+        <v>244</v>
+      </c>
+      <c r="N24" t="s" s="2">
+        <v>245</v>
+      </c>
       <c r="O24" t="s" s="2">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q24" s="2"/>
       <c r="R24" t="s" s="2">
-        <v>239</v>
+        <v>77</v>
       </c>
       <c r="S24" t="s" s="2">
         <v>77</v>
@@ -4386,28 +4079,28 @@
         <v>77</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH24" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI24" t="s" s="2">
-        <v>77</v>
+        <v>247</v>
       </c>
       <c r="AJ24" t="s" s="2">
-        <v>99</v>
+        <v>248</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="AM24" t="s" s="2">
-        <v>77</v>
+        <v>251</v>
       </c>
       <c r="AN24" t="s" s="2">
         <v>77</v>
@@ -4415,10 +4108,10 @@
     </row>
     <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
-        <v>243</v>
+        <v>252</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -4441,17 +4134,17 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>163</v>
+        <v>253</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>245</v>
+        <v>254</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>246</v>
+        <v>255</v>
       </c>
       <c r="N25" s="2"/>
       <c r="O25" t="s" s="2">
-        <v>247</v>
+        <v>256</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>77</v>
@@ -4500,7 +4193,7 @@
         <v>77</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>78</v>
@@ -4515,13 +4208,13 @@
         <v>99</v>
       </c>
       <c r="AK25" t="s" s="2">
-        <v>249</v>
+        <v>173</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>250</v>
+        <v>257</v>
       </c>
       <c r="AM25" t="s" s="2">
-        <v>77</v>
+        <v>188</v>
       </c>
       <c r="AN25" t="s" s="2">
         <v>77</v>
@@ -4529,10 +4222,10 @@
     </row>
     <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
-        <v>251</v>
+        <v>258</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -4543,7 +4236,7 @@
         <v>78</v>
       </c>
       <c r="G26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H26" t="s" s="2">
         <v>77</v>
@@ -4552,22 +4245,22 @@
         <v>77</v>
       </c>
       <c r="J26" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>77</v>
@@ -4622,7 +4315,7 @@
         <v>78</v>
       </c>
       <c r="AH26" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI26" t="s" s="2">
         <v>77</v>
@@ -4631,10 +4324,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>259</v>
+        <v>77</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>77</v>
@@ -4645,10 +4338,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>262</v>
+        <v>265</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -4668,23 +4361,19 @@
         <v>77</v>
       </c>
       <c r="J27" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>263</v>
+        <v>192</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>264</v>
-      </c>
-      <c r="N27" t="s" s="2">
-        <v>265</v>
-      </c>
-      <c r="O27" t="s" s="2">
-        <v>266</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N27" s="2"/>
+      <c r="O27" s="2"/>
       <c r="P27" t="s" s="2">
         <v>77</v>
       </c>
@@ -4732,7 +4421,7 @@
         <v>77</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>267</v>
+        <v>194</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -4744,13 +4433,13 @@
         <v>77</v>
       </c>
       <c r="AJ27" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK27" t="s" s="2">
-        <v>268</v>
+        <v>77</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>269</v>
+        <v>188</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>77</v>
@@ -4761,21 +4450,21 @@
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>270</v>
+        <v>266</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>271</v>
+        <v>266</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E28" s="2"/>
       <c r="F28" t="s" s="2">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="G28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H28" t="s" s="2">
         <v>77</v>
@@ -4784,35 +4473,33 @@
         <v>77</v>
       </c>
       <c r="J28" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>101</v>
+        <v>133</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>272</v>
+        <v>134</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>273</v>
+        <v>196</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>274</v>
-      </c>
-      <c r="O28" t="s" s="2">
-        <v>275</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O28" s="2"/>
       <c r="P28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="Q28" s="2"/>
       <c r="R28" t="s" s="2">
-        <v>276</v>
+        <v>77</v>
       </c>
       <c r="S28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="T28" t="s" s="2">
-        <v>277</v>
+        <v>77</v>
       </c>
       <c r="U28" t="s" s="2">
         <v>77</v>
@@ -4848,28 +4535,28 @@
         <v>77</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>278</v>
+        <v>199</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH28" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI28" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ28" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>279</v>
+        <v>77</v>
       </c>
       <c r="AL28" t="s" s="2">
-        <v>280</v>
+        <v>188</v>
       </c>
       <c r="AM28" t="s" s="2">
-        <v>281</v>
+        <v>77</v>
       </c>
       <c r="AN28" t="s" s="2">
         <v>77</v>
@@ -4877,44 +4564,46 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>282</v>
+        <v>267</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>283</v>
+        <v>267</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
-        <v>77</v>
+        <v>268</v>
       </c>
       <c r="E29" s="2"/>
       <c r="F29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I29" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="J29" t="s" s="2">
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>163</v>
+        <v>133</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>284</v>
+        <v>269</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>285</v>
+        <v>270</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>286</v>
-      </c>
-      <c r="O29" s="2"/>
+        <v>136</v>
+      </c>
+      <c r="O29" t="s" s="2">
+        <v>142</v>
+      </c>
       <c r="P29" t="s" s="2">
         <v>77</v>
       </c>
@@ -4926,7 +4615,7 @@
         <v>77</v>
       </c>
       <c r="T29" t="s" s="2">
-        <v>287</v>
+        <v>77</v>
       </c>
       <c r="U29" t="s" s="2">
         <v>77</v>
@@ -4962,39 +4651,39 @@
         <v>77</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>288</v>
+        <v>271</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH29" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI29" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ29" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>289</v>
+        <v>77</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>290</v>
+        <v>130</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>291</v>
+        <v>77</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>77</v>
       </c>
     </row>
-    <row r="30" hidden="true">
+    <row r="30">
       <c r="A30" t="s" s="2">
-        <v>292</v>
+        <v>272</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>293</v>
+        <v>272</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5008,25 +4697,27 @@
         <v>87</v>
       </c>
       <c r="H30" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I30" t="s" s="2">
         <v>77</v>
       </c>
       <c r="J30" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>294</v>
+        <v>178</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>295</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>296</v>
+        <v>274</v>
       </c>
       <c r="N30" s="2"/>
-      <c r="O30" s="2"/>
+      <c r="O30" t="s" s="2">
+        <v>275</v>
+      </c>
       <c r="P30" t="s" s="2">
         <v>77</v>
       </c>
@@ -5050,13 +4741,13 @@
         <v>77</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>77</v>
+        <v>276</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>77</v>
+        <v>277</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>77</v>
+        <v>278</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>77</v>
@@ -5074,7 +4765,7 @@
         <v>77</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>297</v>
+        <v>272</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5089,13 +4780,13 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>298</v>
+        <v>77</v>
       </c>
       <c r="AL30" t="s" s="2">
-        <v>299</v>
+        <v>279</v>
       </c>
       <c r="AM30" t="s" s="2">
-        <v>300</v>
+        <v>77</v>
       </c>
       <c r="AN30" t="s" s="2">
         <v>77</v>
@@ -5103,10 +4794,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>301</v>
+        <v>280</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>302</v>
+        <v>280</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5126,20 +4817,18 @@
         <v>77</v>
       </c>
       <c r="J31" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>303</v>
+        <v>191</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>304</v>
+        <v>192</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>305</v>
-      </c>
-      <c r="N31" t="s" s="2">
-        <v>306</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="N31" s="2"/>
       <c r="O31" s="2"/>
       <c r="P31" t="s" s="2">
         <v>77</v>
@@ -5188,7 +4877,7 @@
         <v>77</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>307</v>
+        <v>194</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5200,16 +4889,16 @@
         <v>77</v>
       </c>
       <c r="AJ31" t="s" s="2">
-        <v>99</v>
+        <v>77</v>
       </c>
       <c r="AK31" t="s" s="2">
-        <v>308</v>
+        <v>77</v>
       </c>
       <c r="AL31" t="s" s="2">
-        <v>309</v>
+        <v>188</v>
       </c>
       <c r="AM31" t="s" s="2">
-        <v>310</v>
+        <v>77</v>
       </c>
       <c r="AN31" t="s" s="2">
         <v>77</v>
@@ -5217,52 +4906,48 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>311</v>
+        <v>281</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
-        <v>77</v>
+        <v>132</v>
       </c>
       <c r="E32" s="2"/>
       <c r="F32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="G32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="I32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="J32" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>253</v>
+        <v>133</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>312</v>
+        <v>134</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>313</v>
+        <v>196</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>314</v>
-      </c>
-      <c r="O32" t="s" s="2">
-        <v>315</v>
-      </c>
+        <v>136</v>
+      </c>
+      <c r="O32" s="2"/>
       <c r="P32" t="s" s="2">
         <v>77</v>
       </c>
-      <c r="Q32" t="s" s="2">
-        <v>316</v>
-      </c>
+      <c r="Q32" s="2"/>
       <c r="R32" t="s" s="2">
         <v>77</v>
       </c>
@@ -5294,51 +4979,51 @@
         <v>77</v>
       </c>
       <c r="AB32" t="s" s="2">
-        <v>77</v>
+        <v>197</v>
       </c>
       <c r="AC32" t="s" s="2">
-        <v>77</v>
+        <v>198</v>
       </c>
       <c r="AD32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AE32" t="s" s="2">
-        <v>77</v>
+        <v>151</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>311</v>
+        <v>199</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH32" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI32" t="s" s="2">
         <v>77</v>
       </c>
       <c r="AJ32" t="s" s="2">
-        <v>99</v>
+        <v>138</v>
       </c>
       <c r="AK32" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AL32" t="s" s="2">
-        <v>318</v>
+        <v>188</v>
       </c>
       <c r="AM32" t="s" s="2">
-        <v>319</v>
+        <v>77</v>
       </c>
       <c r="AN32" t="s" s="2">
-        <v>320</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="33" hidden="true">
+    <row r="33">
       <c r="A33" t="s" s="2">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>321</v>
+        <v>282</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5352,7 +5037,7 @@
         <v>79</v>
       </c>
       <c r="H33" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I33" t="s" s="2">
         <v>77</v>
@@ -5361,19 +5046,19 @@
         <v>88</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>188</v>
+        <v>201</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>322</v>
+        <v>202</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>323</v>
+        <v>203</v>
       </c>
       <c r="N33" t="s" s="2">
-        <v>324</v>
+        <v>204</v>
       </c>
       <c r="O33" t="s" s="2">
-        <v>325</v>
+        <v>205</v>
       </c>
       <c r="P33" t="s" s="2">
         <v>77</v>
@@ -5398,13 +5083,13 @@
         <v>77</v>
       </c>
       <c r="X33" t="s" s="2">
-        <v>326</v>
+        <v>77</v>
       </c>
       <c r="Y33" t="s" s="2">
-        <v>327</v>
+        <v>77</v>
       </c>
       <c r="Z33" t="s" s="2">
-        <v>328</v>
+        <v>77</v>
       </c>
       <c r="AA33" t="s" s="2">
         <v>77</v>
@@ -5422,7 +5107,7 @@
         <v>77</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>321</v>
+        <v>206</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>78</v>
@@ -5437,24 +5122,24 @@
         <v>99</v>
       </c>
       <c r="AK33" t="s" s="2">
-        <v>329</v>
+        <v>207</v>
       </c>
       <c r="AL33" t="s" s="2">
-        <v>330</v>
+        <v>208</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AN33" t="s" s="2">
-        <v>331</v>
+        <v>77</v>
       </c>
     </row>
-    <row r="34" hidden="true">
+    <row r="34">
       <c r="A34" t="s" s="2">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>332</v>
+        <v>283</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5468,7 +5153,7 @@
         <v>87</v>
       </c>
       <c r="H34" t="s" s="2">
-        <v>77</v>
+        <v>88</v>
       </c>
       <c r="I34" t="s" s="2">
         <v>77</v>
@@ -5477,19 +5162,19 @@
         <v>88</v>
       </c>
       <c r="K34" t="s" s="2">
-        <v>163</v>
+        <v>191</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>333</v>
+        <v>210</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>334</v>
+        <v>211</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>335</v>
+        <v>212</v>
       </c>
       <c r="O34" t="s" s="2">
-        <v>336</v>
+        <v>213</v>
       </c>
       <c r="P34" t="s" s="2">
         <v>77</v>
@@ -5538,7 +5223,7 @@
         <v>77</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>332</v>
+        <v>214</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>78</v>
@@ -5547,19 +5232,19 @@
         <v>87</v>
       </c>
       <c r="AI34" t="s" s="2">
-        <v>152</v>
+        <v>77</v>
       </c>
       <c r="AJ34" t="s" s="2">
         <v>99</v>
       </c>
       <c r="AK34" t="s" s="2">
-        <v>337</v>
+        <v>215</v>
       </c>
       <c r="AL34" t="s" s="2">
-        <v>338</v>
+        <v>216</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>339</v>
+        <v>77</v>
       </c>
       <c r="AN34" t="s" s="2">
         <v>77</v>
@@ -5567,10 +5252,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -5581,7 +5266,7 @@
         <v>78</v>
       </c>
       <c r="G35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H35" t="s" s="2">
         <v>77</v>
@@ -5593,19 +5278,17 @@
         <v>77</v>
       </c>
       <c r="K35" t="s" s="2">
-        <v>163</v>
+        <v>285</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>341</v>
+        <v>286</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>342</v>
-      </c>
-      <c r="N35" t="s" s="2">
-        <v>343</v>
-      </c>
+        <v>287</v>
+      </c>
+      <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>344</v>
+        <v>288</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>77</v>
@@ -5654,13 +5337,13 @@
         <v>77</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>340</v>
+        <v>284</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH35" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI35" t="s" s="2">
         <v>77</v>
@@ -5669,10 +5352,10 @@
         <v>99</v>
       </c>
       <c r="AK35" t="s" s="2">
-        <v>77</v>
+        <v>289</v>
       </c>
       <c r="AL35" t="s" s="2">
-        <v>338</v>
+        <v>290</v>
       </c>
       <c r="AM35" t="s" s="2">
         <v>77</v>
@@ -5683,10 +5366,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -5709,19 +5392,17 @@
         <v>77</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>346</v>
+        <v>231</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>347</v>
+        <v>292</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>348</v>
-      </c>
-      <c r="N36" t="s" s="2">
-        <v>349</v>
-      </c>
+        <v>293</v>
+      </c>
+      <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>350</v>
+        <v>294</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>77</v>
@@ -5770,7 +5451,7 @@
         <v>77</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>345</v>
+        <v>291</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>78</v>
@@ -5779,19 +5460,19 @@
         <v>79</v>
       </c>
       <c r="AI36" t="s" s="2">
-        <v>351</v>
+        <v>77</v>
       </c>
       <c r="AJ36" t="s" s="2">
-        <v>352</v>
+        <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>353</v>
+        <v>295</v>
       </c>
       <c r="AL36" t="s" s="2">
-        <v>354</v>
+        <v>296</v>
       </c>
       <c r="AM36" t="s" s="2">
-        <v>355</v>
+        <v>77</v>
       </c>
       <c r="AN36" t="s" s="2">
         <v>77</v>
@@ -5799,10 +5480,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -5813,7 +5494,7 @@
         <v>78</v>
       </c>
       <c r="G37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="H37" t="s" s="2">
         <v>88</v>
@@ -5825,19 +5506,17 @@
         <v>77</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>357</v>
+        <v>242</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>358</v>
+        <v>298</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>359</v>
-      </c>
-      <c r="N37" t="s" s="2">
-        <v>360</v>
-      </c>
+        <v>299</v>
+      </c>
+      <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>361</v>
+        <v>300</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>77</v>
@@ -5886,28 +5565,28 @@
         <v>77</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>356</v>
+        <v>297</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH37" t="s" s="2">
-        <v>79</v>
+        <v>87</v>
       </c>
       <c r="AI37" t="s" s="2">
-        <v>362</v>
+        <v>77</v>
       </c>
       <c r="AJ37" t="s" s="2">
-        <v>363</v>
+        <v>99</v>
       </c>
       <c r="AK37" t="s" s="2">
-        <v>364</v>
+        <v>301</v>
       </c>
       <c r="AL37" t="s" s="2">
-        <v>365</v>
+        <v>302</v>
       </c>
       <c r="AM37" t="s" s="2">
-        <v>366</v>
+        <v>77</v>
       </c>
       <c r="AN37" t="s" s="2">
         <v>77</v>
@@ -5915,10 +5594,10 @@
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -5929,7 +5608,7 @@
         <v>78</v>
       </c>
       <c r="G38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="H38" t="s" s="2">
         <v>77</v>
@@ -5938,20 +5617,20 @@
         <v>77</v>
       </c>
       <c r="J38" t="s" s="2">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>368</v>
+        <v>305</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>369</v>
+        <v>306</v>
       </c>
       <c r="N38" s="2"/>
       <c r="O38" t="s" s="2">
-        <v>370</v>
+        <v>307</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>77</v>
@@ -6000,13 +5679,13 @@
         <v>77</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>367</v>
+        <v>303</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
       </c>
       <c r="AH38" t="s" s="2">
-        <v>87</v>
+        <v>79</v>
       </c>
       <c r="AI38" t="s" s="2">
         <v>77</v>
@@ -6015,1048 +5694,20 @@
         <v>99</v>
       </c>
       <c r="AK38" t="s" s="2">
-        <v>317</v>
+        <v>77</v>
       </c>
       <c r="AL38" t="s" s="2">
-        <v>371</v>
+        <v>188</v>
       </c>
       <c r="AM38" t="s" s="2">
-        <v>167</v>
+        <v>77</v>
       </c>
       <c r="AN38" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="39" hidden="true">
-      <c r="A39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="B39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="C39" s="2"/>
-      <c r="D39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E39" s="2"/>
-      <c r="F39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K39" t="s" s="2">
-        <v>373</v>
-      </c>
-      <c r="L39" t="s" s="2">
-        <v>374</v>
-      </c>
-      <c r="M39" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="N39" t="s" s="2">
-        <v>376</v>
-      </c>
-      <c r="O39" t="s" s="2">
-        <v>377</v>
-      </c>
-      <c r="P39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q39" s="2"/>
-      <c r="R39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF39" t="s" s="2">
-        <v>372</v>
-      </c>
-      <c r="AG39" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH39" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ39" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL39" t="s" s="2">
-        <v>378</v>
-      </c>
-      <c r="AM39" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN39" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="40" hidden="true">
-      <c r="A40" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="B40" t="s" s="2">
-        <v>379</v>
-      </c>
-      <c r="C40" s="2"/>
-      <c r="D40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E40" s="2"/>
-      <c r="F40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K40" t="s" s="2">
-        <v>163</v>
-      </c>
-      <c r="L40" t="s" s="2">
-        <v>164</v>
-      </c>
-      <c r="M40" t="s" s="2">
-        <v>165</v>
-      </c>
-      <c r="N40" s="2"/>
-      <c r="O40" s="2"/>
-      <c r="P40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q40" s="2"/>
-      <c r="R40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF40" t="s" s="2">
-        <v>166</v>
-      </c>
-      <c r="AG40" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH40" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AK40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL40" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM40" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN40" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="41" hidden="true">
-      <c r="A41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="B41" t="s" s="2">
-        <v>380</v>
-      </c>
-      <c r="C41" s="2"/>
-      <c r="D41" t="s" s="2">
-        <v>132</v>
-      </c>
-      <c r="E41" s="2"/>
-      <c r="F41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K41" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L41" t="s" s="2">
-        <v>134</v>
-      </c>
-      <c r="M41" t="s" s="2">
-        <v>170</v>
-      </c>
-      <c r="N41" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O41" s="2"/>
-      <c r="P41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q41" s="2"/>
-      <c r="R41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF41" t="s" s="2">
-        <v>173</v>
-      </c>
-      <c r="AG41" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH41" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ41" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL41" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM41" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN41" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="42" hidden="true">
-      <c r="A42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="B42" t="s" s="2">
-        <v>381</v>
-      </c>
-      <c r="C42" s="2"/>
-      <c r="D42" t="s" s="2">
-        <v>382</v>
-      </c>
-      <c r="E42" s="2"/>
-      <c r="F42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="J42" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="K42" t="s" s="2">
-        <v>133</v>
-      </c>
-      <c r="L42" t="s" s="2">
-        <v>383</v>
-      </c>
-      <c r="M42" t="s" s="2">
-        <v>384</v>
-      </c>
-      <c r="N42" t="s" s="2">
-        <v>136</v>
-      </c>
-      <c r="O42" t="s" s="2">
-        <v>142</v>
-      </c>
-      <c r="P42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q42" s="2"/>
-      <c r="R42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF42" t="s" s="2">
-        <v>385</v>
-      </c>
-      <c r="AG42" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH42" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ42" t="s" s="2">
-        <v>138</v>
-      </c>
-      <c r="AK42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL42" t="s" s="2">
-        <v>130</v>
-      </c>
-      <c r="AM42" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN42" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="43" hidden="true">
-      <c r="A43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="B43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="C43" s="2"/>
-      <c r="D43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E43" s="2"/>
-      <c r="F43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K43" t="s" s="2">
-        <v>188</v>
-      </c>
-      <c r="L43" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="M43" t="s" s="2">
-        <v>388</v>
-      </c>
-      <c r="N43" s="2"/>
-      <c r="O43" t="s" s="2">
-        <v>389</v>
-      </c>
-      <c r="P43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q43" s="2"/>
-      <c r="R43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X43" t="s" s="2">
-        <v>193</v>
-      </c>
-      <c r="Y43" t="s" s="2">
-        <v>390</v>
-      </c>
-      <c r="Z43" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AA43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF43" t="s" s="2">
-        <v>386</v>
-      </c>
-      <c r="AG43" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH43" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ43" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL43" t="s" s="2">
-        <v>392</v>
-      </c>
-      <c r="AM43" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN43" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="44" hidden="true">
-      <c r="A44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="B44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="C44" s="2"/>
-      <c r="D44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E44" s="2"/>
-      <c r="F44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K44" t="s" s="2">
-        <v>394</v>
-      </c>
-      <c r="L44" t="s" s="2">
-        <v>395</v>
-      </c>
-      <c r="M44" t="s" s="2">
-        <v>396</v>
-      </c>
-      <c r="N44" s="2"/>
-      <c r="O44" t="s" s="2">
-        <v>397</v>
-      </c>
-      <c r="P44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q44" s="2"/>
-      <c r="R44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF44" t="s" s="2">
-        <v>393</v>
-      </c>
-      <c r="AG44" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH44" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ44" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK44" t="s" s="2">
-        <v>398</v>
-      </c>
-      <c r="AL44" t="s" s="2">
-        <v>399</v>
-      </c>
-      <c r="AM44" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN44" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="45" hidden="true">
-      <c r="A45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="B45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="C45" s="2"/>
-      <c r="D45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E45" s="2"/>
-      <c r="F45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K45" t="s" s="2">
-        <v>346</v>
-      </c>
-      <c r="L45" t="s" s="2">
-        <v>401</v>
-      </c>
-      <c r="M45" t="s" s="2">
-        <v>402</v>
-      </c>
-      <c r="N45" s="2"/>
-      <c r="O45" t="s" s="2">
-        <v>403</v>
-      </c>
-      <c r="P45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q45" s="2"/>
-      <c r="R45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF45" t="s" s="2">
-        <v>400</v>
-      </c>
-      <c r="AG45" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH45" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ45" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK45" t="s" s="2">
-        <v>404</v>
-      </c>
-      <c r="AL45" t="s" s="2">
-        <v>405</v>
-      </c>
-      <c r="AM45" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN45" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="B46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="C46" s="2"/>
-      <c r="D46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E46" s="2"/>
-      <c r="F46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="H46" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="I46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K46" t="s" s="2">
-        <v>357</v>
-      </c>
-      <c r="L46" t="s" s="2">
-        <v>407</v>
-      </c>
-      <c r="M46" t="s" s="2">
-        <v>408</v>
-      </c>
-      <c r="N46" s="2"/>
-      <c r="O46" t="s" s="2">
-        <v>409</v>
-      </c>
-      <c r="P46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q46" s="2"/>
-      <c r="R46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF46" t="s" s="2">
-        <v>406</v>
-      </c>
-      <c r="AG46" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH46" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="AI46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ46" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK46" t="s" s="2">
-        <v>410</v>
-      </c>
-      <c r="AL46" t="s" s="2">
-        <v>411</v>
-      </c>
-      <c r="AM46" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN46" t="s" s="2">
-        <v>77</v>
-      </c>
-    </row>
-    <row r="47" hidden="true">
-      <c r="A47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="B47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="C47" s="2"/>
-      <c r="D47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="E47" s="2"/>
-      <c r="F47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="G47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="H47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="I47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="J47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="K47" t="s" s="2">
-        <v>413</v>
-      </c>
-      <c r="L47" t="s" s="2">
-        <v>414</v>
-      </c>
-      <c r="M47" t="s" s="2">
-        <v>415</v>
-      </c>
-      <c r="N47" s="2"/>
-      <c r="O47" t="s" s="2">
-        <v>416</v>
-      </c>
-      <c r="P47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Q47" s="2"/>
-      <c r="R47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="S47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="T47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="U47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="V47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="W47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="X47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Y47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="Z47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AA47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AB47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AC47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AD47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AE47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AF47" t="s" s="2">
-        <v>412</v>
-      </c>
-      <c r="AG47" t="s" s="2">
-        <v>78</v>
-      </c>
-      <c r="AH47" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AI47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AJ47" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="AK47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AL47" t="s" s="2">
-        <v>167</v>
-      </c>
-      <c r="AM47" t="s" s="2">
-        <v>77</v>
-      </c>
-      <c r="AN47" t="s" s="2">
         <v>77</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:AN47">
+  <autoFilter ref="A1:AN38">
     <filterColumn colId="7">
       <customFilters>
         <customFilter operator="notEqual" val=" "/>
@@ -7066,7 +5717,7 @@
       <filters blank="true"/>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="A2:AI46">
+  <conditionalFormatting sqref="A2:AI37">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>$G2&lt;&gt;"Y"</formula>
     </cfRule>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:32:03+00:00</t>
+    <t>2026-04-10T05:44:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T05:44:36+00:00</t>
+    <t>2026-05-26T03:51:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T03:51:01+00:00</t>
+    <t>2026-05-26T04:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/dev/StructureDefinition-ph-core-organization.xlsx
+++ b/dev/StructureDefinition-ph-core-organization.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-26T04:00:40+00:00</t>
+    <t>2026-05-26T04:36:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
